--- a/EmployeeBillableData_9.xlsx
+++ b/EmployeeBillableData_9.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="88">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -197,58 +197,49 @@
     <t>ApMoSys-HR</t>
   </si>
   <si>
-    <t>A-250124</t>
-  </si>
-  <si>
-    <t>Akanksha Agrawal</t>
-  </si>
-  <si>
-    <t>akanksha.agrawal@apmosysuat1.com</t>
+    <t>A-250230</t>
+  </si>
+  <si>
+    <t>Shruti Sanjay Damne</t>
+  </si>
+  <si>
+    <t>hrd2@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250243</t>
+  </si>
+  <si>
+    <t>Mangalya Panikar</t>
+  </si>
+  <si>
+    <t>legal@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Anand Kishore</t>
+  </si>
+  <si>
+    <t>Legal Compliance</t>
+  </si>
+  <si>
+    <t>A-1533</t>
+  </si>
+  <si>
+    <t>lituja.mishra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Sangeeta Padhy</t>
+  </si>
+  <si>
+    <t>ApMoSys-HR,Apprentice Training</t>
+  </si>
+  <si>
+    <t>A-25001</t>
+  </si>
+  <si>
+    <t>parag.sawant@apmosysuat1.com</t>
   </si>
   <si>
     <t>TRAINING-HR</t>
-  </si>
-  <si>
-    <t>A-250230</t>
-  </si>
-  <si>
-    <t>Shruti Sanjay Damne</t>
-  </si>
-  <si>
-    <t>hrd2@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-250243</t>
-  </si>
-  <si>
-    <t>Mangalya Panikar</t>
-  </si>
-  <si>
-    <t>legal@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Anand Kishore</t>
-  </si>
-  <si>
-    <t>Legal Compliance</t>
-  </si>
-  <si>
-    <t>A-1533</t>
-  </si>
-  <si>
-    <t>lituja.mishra@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Sangeeta Padhy</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR,Apprentice Training</t>
-  </si>
-  <si>
-    <t>A-25001</t>
-  </si>
-  <si>
-    <t>parag.sawant@apmosysuat1.com</t>
   </si>
   <si>
     <t>A-4</t>
@@ -363,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
@@ -782,13 +773,13 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
         <v>30</v>
@@ -796,13 +787,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -814,13 +805,13 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
@@ -828,10 +819,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>70</v>
@@ -863,7 +854,7 @@
         <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>74</v>
@@ -878,13 +869,13 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
         <v>75</v>
-      </c>
-      <c r="H16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" t="s">
-        <v>76</v>
       </c>
       <c r="J16" t="s">
         <v>30</v>
@@ -892,10 +883,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
         <v>77</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>78</v>
@@ -910,45 +901,45 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" t="s">
-        <v>30</v>
-      </c>
+      <c r="I17"/>
+      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
-      <c r="I18"/>
-      <c r="J18"/>
+      <c r="I18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -961,10 +952,10 @@
         <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
@@ -976,7 +967,7 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J19" t="s">
         <v>30</v>
@@ -987,22 +978,22 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
         <v>87</v>
       </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1011,38 +1002,6 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" t="s">
         <v>30</v>
       </c>
     </row>

--- a/EmployeeBillableData_9.xlsx
+++ b/EmployeeBillableData_9.xlsx
@@ -587,7 +587,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>

--- a/EmployeeBillableData_9.xlsx
+++ b/EmployeeBillableData_9.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="84">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -53,10 +53,10 @@
     <t>hrm2@apmosysuat1.com</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>TNM</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>InternalRNDProducts</t>
   </si>
   <si>
     <t>HR</t>
@@ -68,214 +68,202 @@
     <t>Lituja Mishra</t>
   </si>
   <si>
-    <t>ApMoSys-HR,DEV-TNM-ertyu-real time test -alaka -18.6,DEV-TNM-ertyu-real time test -alaka -19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aniruddha,ApMoSys</t>
+    <t>ApMoSys-HR</t>
+  </si>
+  <si>
+    <t>ApMoSys</t>
+  </si>
+  <si>
+    <t>A-23143</t>
+  </si>
+  <si>
+    <t>Rajani Tambe</t>
+  </si>
+  <si>
+    <t>hrd3@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260194</t>
+  </si>
+  <si>
+    <t>S Sandhya</t>
+  </si>
+  <si>
+    <t>sandhya.s@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-1533</t>
+  </si>
+  <si>
+    <t>lituja.mishra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Sangeeta Padhy</t>
+  </si>
+  <si>
+    <t>A-25001</t>
+  </si>
+  <si>
+    <t>Parag Sawant</t>
+  </si>
+  <si>
+    <t>parag.sawant@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>TRAINING-HR</t>
+  </si>
+  <si>
+    <t>A-4</t>
+  </si>
+  <si>
+    <t>Admin Four</t>
+  </si>
+  <si>
+    <t>admin4@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Admin1</t>
+  </si>
+  <si>
+    <t>A-250266</t>
+  </si>
+  <si>
+    <t>Siddharth Shilimkar</t>
+  </si>
+  <si>
+    <t>srmgr1@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260213</t>
+  </si>
+  <si>
+    <t>Mausimi Sardar</t>
+  </si>
+  <si>
+    <t>srmgr3@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-22253</t>
+  </si>
+  <si>
+    <t>Sarita Kumari Mishra</t>
+  </si>
+  <si>
+    <t>sarita.mishra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-22277</t>
+  </si>
+  <si>
+    <t>Rajyalaxmi Padhi</t>
+  </si>
+  <si>
+    <t>rajyalaxmi.padhi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240213</t>
+  </si>
+  <si>
+    <t>Vini Thomas</t>
+  </si>
+  <si>
+    <t>srmgr2@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Rumi Saha</t>
+  </si>
+  <si>
+    <t>A-250502</t>
+  </si>
+  <si>
+    <t>rumi.saha@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250416</t>
+  </si>
+  <si>
+    <t>Ayusha Vilas Khandekar</t>
+  </si>
+  <si>
+    <t>ayusha.khandekar@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240264</t>
+  </si>
+  <si>
+    <t>Johan Fernandes</t>
+  </si>
+  <si>
+    <t>johan.fernandes@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-23153</t>
+  </si>
+  <si>
+    <t>Lipsa Mohanty</t>
+  </si>
+  <si>
+    <t>hrd1@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240327</t>
+  </si>
+  <si>
+    <t>Mangesh Sunil Mane</t>
+  </si>
+  <si>
+    <t>hrd4@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250230</t>
+  </si>
+  <si>
+    <t>Shruti Sanjay Damne</t>
+  </si>
+  <si>
+    <t>hrd2@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260009</t>
+  </si>
+  <si>
+    <t>Priyesh Madhukar Kurangale</t>
+  </si>
+  <si>
+    <t>hrd@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260090</t>
+  </si>
+  <si>
+    <t>Suchitra Deshpande</t>
+  </si>
+  <si>
+    <t>hrd6@apmosysuat1.com</t>
   </si>
   <si>
     <t>A-2388</t>
   </si>
   <si>
-    <t>Gudimetla V S</t>
+    <t>Gudimetla V S Eswar</t>
   </si>
   <si>
     <t>hrm1@apmosysuat1.com</t>
   </si>
   <si>
-    <t>Parag Sawant</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR,DEV-TNM-ertyu-real time test -alaka -18.4,DEV-TNM-ertyu-real time test -alaka -19.1</t>
-  </si>
-  <si>
     <t>A-23232</t>
   </si>
   <si>
     <t>suparna.mishra@apmosysuat1.com</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Bench</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR,DEV-BENCH</t>
-  </si>
-  <si>
-    <t>ApMoSys</t>
-  </si>
-  <si>
-    <t>A-22253</t>
-  </si>
-  <si>
-    <t>Sarita Kumari Mishra</t>
-  </si>
-  <si>
-    <t>sarita.mishra@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>DEV-BENCH</t>
-  </si>
-  <si>
-    <t>A-22277</t>
-  </si>
-  <si>
-    <t>Rajyalaxmi Padhi</t>
-  </si>
-  <si>
-    <t>rajyalaxmi.padhi@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-2392</t>
-  </si>
-  <si>
-    <t>Priyanka Bagave</t>
-  </si>
-  <si>
-    <t>hrd@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-23143</t>
-  </si>
-  <si>
-    <t>Rajani Tambe</t>
-  </si>
-  <si>
-    <t>hrd3@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-23153</t>
-  </si>
-  <si>
-    <t>Lipsa Mohanty</t>
-  </si>
-  <si>
-    <t>hrd1@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Siddharth Shilimkar</t>
-  </si>
-  <si>
-    <t>A-23264</t>
-  </si>
-  <si>
-    <t>Maithili Patole</t>
-  </si>
-  <si>
-    <t>hrd5@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR,CO-FT-AT-TNM-AXISBANK-BSG-TCoE</t>
-  </si>
-  <si>
-    <t>ApMoSys,AXIS BANK</t>
-  </si>
-  <si>
-    <t>A-240327</t>
-  </si>
-  <si>
-    <t>Mangesh Sunil Mane</t>
-  </si>
-  <si>
-    <t>hrd4@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-250063</t>
-  </si>
-  <si>
-    <t>Rupali Surve</t>
-  </si>
-  <si>
-    <t>hrd6@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>InternalRNDProducts</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR</t>
-  </si>
-  <si>
-    <t>A-250230</t>
-  </si>
-  <si>
-    <t>Shruti Sanjay Damne</t>
-  </si>
-  <si>
-    <t>hrd2@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-250243</t>
-  </si>
-  <si>
-    <t>Mangalya Panikar</t>
-  </si>
-  <si>
-    <t>legal@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Anand Kishore</t>
-  </si>
-  <si>
-    <t>Legal Compliance</t>
-  </si>
-  <si>
-    <t>A-1533</t>
-  </si>
-  <si>
-    <t>lituja.mishra@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Sangeeta Padhy</t>
-  </si>
-  <si>
-    <t>ApMoSys-HR,Apprentice Training</t>
-  </si>
-  <si>
-    <t>A-25001</t>
-  </si>
-  <si>
-    <t>parag.sawant@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>TRAINING-HR</t>
-  </si>
-  <si>
-    <t>A-4</t>
-  </si>
-  <si>
-    <t>Admin Four</t>
-  </si>
-  <si>
-    <t>admin4@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Admin1</t>
-  </si>
-  <si>
-    <t>A-240264</t>
-  </si>
-  <si>
-    <t>Johan Fernandes</t>
-  </si>
-  <si>
-    <t>johan.fernandes@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-240213</t>
-  </si>
-  <si>
-    <t>Vini Thomas</t>
-  </si>
-  <si>
-    <t>srmgr2@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-250266</t>
-  </si>
-  <si>
-    <t>srmgr1@apmosysuat1.com</t>
+    <t>A-240255</t>
+  </si>
+  <si>
+    <t>Aastha Jain</t>
+  </si>
+  <si>
+    <t>aastha.jain@apmosysuat1.com</t>
   </si>
 </sst>
 </file>
@@ -354,17 +342,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.45703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.62890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.9296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.890625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.1875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.54296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.75390625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="17.6796875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="17.91796875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.09375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="30.0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="40.0" customWidth="true" bestFit="true"/>
   </cols>
@@ -453,13 +441,13 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -467,19 +455,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
@@ -491,181 +479,171 @@
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
-      </c>
+      <c r="I5"/>
+      <c r="J5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E7"/>
       <c r="F7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
-      </c>
+      <c r="I7"/>
+      <c r="J7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -677,279 +655,283 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17"/>
-      <c r="J17"/>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -961,48 +943,144 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>30</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
